--- a/src/main/resources/templates/users_template.xlsx
+++ b/src/main/resources/templates/users_template.xlsx
@@ -19,7 +19,7 @@
   <commentList>
     <comment ref="A1" authorId="0">
       <text>
-        <t>jx:area(bx="A1:F2")</t>
+        <t>jx:area(lastCell="F2")</t>
       </text>
     </comment>
     <comment ref="A2" authorId="0">
